--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R9d44e94339c54409"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R37ce1d4cd27542c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R7b8281edd95542ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Re677012fff0f474f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rf51134aad773451c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rf6a4da8efb48478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R6b8ea13ec3914475"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R3b6c557524d74c5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rc2f8ff8ef2334c44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R838aade67dc046d3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -415,7 +415,7 @@
         <x:v>正确值</x:v>
       </x:c>
       <x:c r="D1" s="9" t="str">
-        <x:v>来源与验证</x:v>
+        <x:v>来源</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" customHeight="1">
@@ -785,7 +785,7 @@
     </x:row>
     <x:row r="6" ht="63" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>reference_members</x:v>
+        <x:v>delivery_paths</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
         <x:v>src/rebuild_webhook_queue.mjs,deliverables/intake_decisions.csv,deliverables/replay_queue.jsonl,deliverables/endpoint_handoff.csv</x:v>
@@ -794,7 +794,7 @@
         <x:v>相对路径逐字匹配</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>reference.zip成员</x:v>
+        <x:v>交付物清单</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1116,7 +1116,7 @@
         <x:v>允许范围</x:v>
       </x:c>
       <x:c r="C1" s="9" t="str">
-        <x:v>不变条件</x:v>
+        <x:v>仍需满足</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" customHeight="1">
